--- a/Globus_School_Management/src/test/resources/TestScriptData.xlsx
+++ b/Globus_School_Management/src/test/resources/TestScriptData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30601"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBEEBCE0-77A5-4D94-BA7F-4A2B0AECF2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D11F8D7-00B6-4A01-A006-1C6C1EEC7F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,7 +240,7 @@
     <t>qrst@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Block A — Room 125 (Floor 1) </t>
+    <t>Block B — Room 101 (Floor 1) </t>
   </si>
   <si>
     <t>6bf9855b-dd71-4107-9aae-e2e98118840f</t>
@@ -270,7 +270,7 @@
     <t>Teacher</t>
   </si>
   <si>
-    <t>02-10-2026</t>
+    <t>2/10/2026</t>
   </si>
   <si>
     <t>title</t>
@@ -279,7 +279,7 @@
     <t>mark</t>
   </si>
   <si>
-    <t xml:space="preserve">subject </t>
+    <t>subject </t>
   </si>
   <si>
     <t>classid</t>
@@ -300,13 +300,13 @@
     <t>C10-SCI</t>
   </si>
   <si>
-    <t>10-10- 2026 17:17</t>
+    <t>10/10/2026  5:17:00 PM</t>
   </si>
   <si>
     <t>abzxsdcvbh</t>
   </si>
   <si>
-    <t xml:space="preserve">Mathematics </t>
+    <t>Mathematics </t>
   </si>
   <si>
     <t>Do all the questions in chapter 6</t>
@@ -324,7 +324,7 @@
     <t>11b732f2-0017-4295-8b89-a7cff498e689</t>
   </si>
   <si>
-    <t xml:space="preserve"> Aarav Sharma (MIS-1A-001)</t>
+    <t> Aarav Sharma (MIS-1A-001)</t>
   </si>
   <si>
     <t>Displine</t>
@@ -342,7 +342,7 @@
     <t>Study Desk</t>
   </si>
   <si>
-    <t xml:space="preserve">Academic </t>
+    <t>Academic </t>
   </si>
 </sst>
 </file>
@@ -420,26 +420,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="22" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -776,15 +765,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="46.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="46.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="46.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="16384" width="46.5703125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -794,404 +777,573 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="296.25">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" s="4" customFormat="1">
-      <c r="A3" s="3" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" s="4" customFormat="1">
-      <c r="A4" s="3" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" s="4" customFormat="1">
-      <c r="A5" s="3" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" s="4" customFormat="1">
-      <c r="A6" s="3" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" s="4" customFormat="1">
-      <c r="A7" s="3" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" s="4" customFormat="1">
-      <c r="A8" s="3" t="s">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" s="4" customFormat="1">
-      <c r="A9" s="3" t="s">
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" s="4" customFormat="1">
-      <c r="A10" s="3" t="s">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" s="4" customFormat="1">
-      <c r="A11" s="3" t="s">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="2" t="s">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="2" t="s">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="2" t="s">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="2" t="s">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="2" t="s">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="2" t="s">
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="2" t="s">
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="2" t="s">
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="2" t="s">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="2" t="s">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="2" t="s">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="2" t="s">
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="29.25">
-      <c r="A29" s="2" t="s">
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="43.5">
-      <c r="A30" s="2" t="s">
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="2" t="s">
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="29.25">
-      <c r="A32" s="2" t="s">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="2" t="s">
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="5" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="2" t="s">
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="6" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="2" t="s">
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>95</v>
       </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D13" r:id="rId1" xr:uid="{680D3DBD-C303-4082-B870-37E8B4AEEA29}"/>
-    <hyperlink ref="B23" r:id="rId2" xr:uid="{665D3712-8A7C-4496-A331-F7E94D993E5F}"/>
+    <hyperlink ref="D13" r:id="rId1" xr:uid="{1A647254-43F4-4DD4-8B91-80119D354DA8}"/>
+    <hyperlink ref="B23" r:id="rId2" xr:uid="{3B85C5CE-5AB9-45B6-8A47-72951F6859C2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
